--- a/reports/jobs_2026-10-16.xlsx
+++ b/reports/jobs_2026-10-16.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I118"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1049,17 +1049,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Graphics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/cambridge/graphics-engineer/33099/96521990288</t>
+          <t>https://www.atlassian.com/company/careers/details/27443</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1092,12 +1092,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Theorem Proving Engineer</t>
+          <t>Application Development Engineer</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1110,7 +1110,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1118,12 +1122,12 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
+          <t>https://www.atlassian.com/company/careers/details/26833</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1135,17 +1139,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Compiler Engineer (Machine Learning)</t>
+          <t>Software Engineer – Full Stack (Loom Billing &amp; Integrations)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1153,7 +1157,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1161,12 +1169,12 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/lund/compiler-engineer-machine-learning/33099/94847322016</t>
+          <t>https://www.atlassian.com/company/careers/details/27431</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1183,12 +1191,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1196,7 +1204,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1204,7 +1216,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27443</t>
+          <t>https://www.atlassian.com/company/careers/details/25561</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1226,12 +1238,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Application Development Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,7 +1263,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26833</t>
+          <t>https://www.atlassian.com/company/careers/details/25539</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1273,12 +1285,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack (Loom Billing &amp; Integrations)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1286,11 +1298,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1298,7 +1306,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27431</t>
+          <t>https://www.atlassian.com/company/careers/details/26758</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1320,12 +1328,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Machine Learning System Engineer</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1345,7 +1353,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25561</t>
+          <t>https://www.atlassian.com/company/careers/details/27388</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1367,12 +1375,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Principle Engineer</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1392,7 +1400,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25539</t>
+          <t>https://www.atlassian.com/company/careers/details/27074</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1414,7 +1422,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>EMEA Field CTO, DX — Engineering Executive Advisor</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1427,7 +1435,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1435,7 +1447,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26758</t>
+          <t>https://www.atlassian.com/company/careers/details/24899</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1457,12 +1469,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning System Engineer</t>
+          <t>Data Engineer, 2027 Graduate U.S</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1470,11 +1482,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1482,7 +1490,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27388</t>
+          <t>https://www.atlassian.com/company/careers/details/25998</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1504,7 +1512,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Principle Engineer</t>
+          <t>Software Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1517,11 +1525,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1529,7 +1533,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27074</t>
+          <t>https://www.atlassian.com/company/careers/details/25813</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1551,12 +1555,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>EMEA Field CTO, DX — Engineering Executive Advisor</t>
+          <t>Machine Learning Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1564,11 +1568,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/24899</t>
+          <t>https://www.atlassian.com/company/careers/details/25999</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Data Engineer, 2027 Graduate U.S</t>
+          <t>Software Engineer, 2027 Graduate Canada</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25998</t>
+          <t>https://www.atlassian.com/company/careers/details/26070</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, 2027 Graduate U.S.</t>
+          <t>Product Design Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1654,7 +1654,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1662,7 +1666,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25813</t>
+          <t>https://www.atlassian.com/company/careers/details/26273</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1684,12 +1688,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, 2027 Graduate U.S.</t>
+          <t>Data Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1697,7 +1701,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1705,7 +1713,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25999</t>
+          <t>https://www.atlassian.com/company/careers/details/26272</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1727,12 +1735,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, 2027 Graduate Canada</t>
+          <t>Product Management Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1740,7 +1748,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1748,7 +1760,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26070</t>
+          <t>https://www.atlassian.com/company/careers/details/26274</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1770,12 +1782,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Product Design Intern, 2027 Summer U.S.</t>
+          <t>Machine Learning Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1783,11 +1795,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1795,7 +1803,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26273</t>
+          <t>https://www.atlassian.com/company/careers/details/26268</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1817,12 +1825,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Data Engineer Intern, 2027 Summer U.S.</t>
+          <t>Research Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1830,11 +1838,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1842,7 +1846,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26272</t>
+          <t>https://www.atlassian.com/company/careers/details/26270</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1864,7 +1868,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Product Management Intern, 2027 Summer U.S.</t>
+          <t>Security Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1877,11 +1881,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26274</t>
+          <t>https://www.atlassian.com/company/careers/details/26267</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Intern, 2027 Summer U.S.</t>
+          <t>Software Engineer Intern, 2027 Canada</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26268</t>
+          <t>https://www.atlassian.com/company/careers/details/26275</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Research Intern, 2027 Summer U.S.</t>
+          <t>AI Demand Intelligence Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1967,7 +1967,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -1975,7 +1979,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26270</t>
+          <t>https://www.atlassian.com/company/careers/details/26843</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1997,7 +2001,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Security Engineer Intern, 2027 Summer U.S.</t>
+          <t>Software Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2018,7 +2022,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26267</t>
+          <t>https://www.atlassian.com/company/careers/details/26266</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2040,12 +2044,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, 2027 Canada</t>
+          <t>Enterprise Security Engineer</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2053,7 +2057,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -2061,7 +2069,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26275</t>
+          <t>https://www.atlassian.com/company/careers/details/27275</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2083,12 +2091,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>AI Demand Intelligence Intern, 2027 Summer U.S.</t>
+          <t>Enterprise Security Engineer</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2108,7 +2116,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26843</t>
+          <t>https://www.atlassian.com/company/careers/details/26986</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2130,12 +2138,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, 2027 Summer U.S.</t>
+          <t>Security Testing Engineer - Penetration Tester</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2143,7 +2151,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Remote or Remote</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -2151,7 +2163,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26266</t>
+          <t>https://www.atlassian.com/company/careers/details/26643</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2168,12 +2180,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Product Security Engineer</t>
+          <t>Product Launch and price new features without waiting on engineering</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2186,11 +2198,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Remote or Remote</t>
-        </is>
-      </c>
+      <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -2198,12 +2206,12 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27475</t>
+          <t>https://www.chargebee.com/solutions/role/product/</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2215,12 +2223,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Security Engineer</t>
+          <t>Growth Test offers, run promotions and lift conversion</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2233,11 +2241,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -2245,12 +2249,12 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27275</t>
+          <t>https://www.chargebee.com/solutions/role/growth/</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2262,12 +2266,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Security Engineer</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2282,7 +2286,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2292,12 +2296,12 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26986</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2309,17 +2313,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Security Testing Engineer - Penetration Tester</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2329,7 +2333,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Remote or Remote</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2339,12 +2343,12 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26643</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2356,12 +2360,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Product Launch and price new features without waiting on engineering</t>
+          <t>Integration &amp; Customisation Engineer-3</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2374,7 +2378,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -2382,12 +2390,12 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/product/</t>
+          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2399,12 +2407,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Growth Test offers, run promotions and lift conversion</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2417,7 +2425,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>India Full-time</t>
+        </is>
+      </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -2425,12 +2437,12 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/growth/</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2447,12 +2459,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2460,11 +2472,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -2472,7 +2480,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2494,12 +2502,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>Software Engineer - 2 (Billing)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2509,7 +2517,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2519,7 +2527,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-700106-software-engineer-2-billing</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2541,7 +2549,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-3</t>
+          <t>Software Engineer - 3 (Voice)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2566,7 +2574,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
+          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2588,7 +2596,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2603,7 +2611,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2613,7 +2621,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2635,12 +2643,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Forward Deployed Engineer - 3</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2648,7 +2656,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -2656,7 +2668,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2678,7 +2690,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Billing)</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2703,7 +2715,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-700106-software-engineer-2-billing</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2725,12 +2737,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Voice)</t>
+          <t>Software Developer - 3 (Voice4Ai-Backend)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2750,7 +2762,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-voice4aibackend</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2772,7 +2784,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2797,7 +2809,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2819,12 +2831,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2844,7 +2856,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2861,17 +2873,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - Washington - Seattle Administration</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2879,11 +2891,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -2891,12 +2899,12 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/seattle-wa/R-110382-2/</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2908,17 +2916,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Voice4Ai-Backend)</t>
+          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - Texas - Austin Administration</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2926,11 +2934,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -2938,12 +2942,12 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-voice4aibackend</t>
+          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/austin-tx/R-110382/</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2955,12 +2959,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2973,11 +2977,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -2985,12 +2985,12 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3002,17 +3002,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3020,11 +3020,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -3032,12 +3028,12 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3049,17 +3045,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - Texas - Austin Administration</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3075,12 +3071,12 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/austin-tx/R-110382/</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3092,17 +3088,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Mobile Engineering Intern - 2027 - Austin, San Jose, Seattle United States - Washington - Seattle Administration</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3110,7 +3106,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/mobile-engineering-intern-2027-austin-san-jose-seattle/seattle-wa/R-110306-2/</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3135,17 +3135,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Mobile Engineering Intern - 2027 - Austin, San Jose, Seattle United States - Texas - Austin Administration</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3153,7 +3153,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -3161,12 +3165,12 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/mobile-engineering-intern-2027-austin-san-jose-seattle/austin-tx/R-110306/</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3178,17 +3182,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - California - San Jose Administration</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3196,7 +3200,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>New Delhi, in</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -3204,12 +3212,12 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/san-jose-ca/R-110382-1/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3221,17 +3229,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - PhD - 2027 - Austin, San Jose, Seattle United States - Washington - Seattle Administration</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3239,7 +3247,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -3247,12 +3259,12 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-phd-2027-austin-san-jose-seattle/seattle-wa/R-110382-2/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3264,12 +3276,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - Masters - 2027 - Austin, San Jose, Seattle United States - Texas - Austin Administration</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3290,12 +3302,12 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-masters-2027-austin-san-jose-seattle/austin-tx/R-110379/</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3307,17 +3319,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - Masters - 2027 - Austin, San Jose, Seattle United States - Washington - Seattle Administration</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3333,12 +3345,12 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-masters-2027-austin-san-jose-seattle/seattle-wa/R-110379-2/</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3350,17 +3362,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Mobile Engineering Intern - 2027 - Austin, San Jose, Seattle United States - California - San Jose Administration</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3368,7 +3380,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu</t>
+        </is>
+      </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -3376,12 +3392,12 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/mobile-engineering-intern-2027-austin-san-jose-seattle/san-jose-ca/R-110306-1/</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3393,17 +3409,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Expedia Group India</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Applied Science Intern - Masters - 2027 - Austin, San Jose, Seattle United States - California - San Jose Administration</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3411,7 +3427,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -3419,12 +3439,12 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/job/applied-science-intern-masters-2027-austin-san-jose-seattle/san-jose-ca/R-110379-1/</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://careers.expediagroup.com/jobs/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3436,17 +3456,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3462,12 +3482,12 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Data-Engineer---AWS_SR-37522</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3479,12 +3499,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>GenAI-Engineer</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3497,7 +3517,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -3505,12 +3529,12 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/GenAI-Engineer_SR-46807</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3522,17 +3546,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3548,12 +3572,12 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Engineer_SR-46455-1</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3565,17 +3589,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Okta India</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3583,7 +3607,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, India</t>
+        </is>
+      </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -3591,12 +3619,12 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-York/MLOps-Engineer_SR-46499-1</t>
+          <t>https://www.okta.com/company/careers/opportunity/8243101?gh_jid=8243101</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://boards.greenhouse.io/okta</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3608,17 +3636,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Open Financial</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Careers Hiring across engineering, design, product, GTM &amp; ops.</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3626,7 +3654,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>India’s 100 th unicorn. C</t>
+        </is>
+      </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -3634,12 +3666,12 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/Data-Engineer_SR-46461-1</t>
+          <t>https://open.money/company/careers.html</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://open.money/careers</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3651,17 +3683,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3677,12 +3709,12 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3694,12 +3726,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Intern - Talent Acquisition</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3712,7 +3744,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Gurugram, Haryana</t>
+        </is>
+      </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -3720,12 +3756,12 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -3737,17 +3773,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3755,7 +3791,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -3763,12 +3803,12 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -3780,12 +3820,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3800,7 +3840,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3810,12 +3850,12 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3827,17 +3867,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3847,7 +3887,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -3857,12 +3897,12 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -3874,17 +3914,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Talent Acquisition Intern - Noida</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3894,7 +3934,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -3904,12 +3944,12 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3921,17 +3961,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3939,11 +3979,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -3951,12 +3987,12 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -3968,17 +4004,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3986,7 +4022,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -3994,12 +4034,12 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4011,12 +4051,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4029,7 +4069,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -4037,12 +4081,12 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4054,17 +4098,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4074,7 +4118,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4084,12 +4128,12 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -4101,17 +4145,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -4119,11 +4163,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -4131,12 +4171,12 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4148,17 +4188,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -4166,7 +4206,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -4174,12 +4218,12 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4191,12 +4235,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>Industrial Trainee</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4211,7 +4255,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4221,12 +4265,12 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4238,17 +4282,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4256,7 +4300,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Bangalore, India</t>
+        </is>
+      </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -4264,12 +4312,12 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -4281,27 +4329,27 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Okta India</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer - Cloud: Azure</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>0-2 years</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, India</t>
+          <t xml:space="preserve">Bangalore </t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -4311,12 +4359,12 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>https://www.okta.com/company/careers/opportunity/8243101?gh_jid=8243101</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/okta</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -4328,17 +4376,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Open Financial</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Careers Hiring across engineering, design, product, GTM &amp; ops.</t>
+          <t>Software Engineer (CPD) - Winter Intern</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4348,7 +4396,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>India’s 100 th unicorn. C</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -4358,12 +4406,12 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>https://open.money/company/careers.html</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://open.money/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -4375,17 +4423,17 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4393,7 +4441,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -4401,12 +4453,12 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -4418,17 +4470,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Intern - Talent Acquisition</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -4438,7 +4490,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana</t>
+          <t>Remote Instructor- Python</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -4448,12 +4500,12 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -4465,12 +4517,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -4483,11 +4535,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -4495,12 +4543,12 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -4512,17 +4560,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>AI Screenplay Writer</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4530,11 +4578,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -4542,12 +4586,12 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -4559,17 +4603,17 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>AI Video Editor</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4577,11 +4621,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -4589,12 +4629,12 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -4606,17 +4646,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Noida</t>
+          <t>AI Sound Designer</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -4624,11 +4664,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -4636,12 +4672,12 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -4653,12 +4689,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -4679,12 +4715,12 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -4696,17 +4732,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -4716,7 +4752,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -4726,12 +4762,12 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -4743,17 +4779,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4763,7 +4799,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -4773,12 +4809,12 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -4790,17 +4826,17 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Intern- Employee Engagement</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4808,11 +4844,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
@@ -4820,12 +4852,12 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -4837,12 +4869,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -4863,12 +4895,12 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -4880,12 +4912,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -4900,7 +4932,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -4910,12 +4942,12 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -4927,17 +4959,17 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Thoughtworks India</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Industrial Trainee</t>
+          <t>Software Procurement Intern</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4947,7 +4979,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Gurgaon, India; Pune, India</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -4957,12 +4989,12 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
+          <t>https://www.thoughtworks.com/careers/jobs/8236673?gh_jid=8236673</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/thoughtworks</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -4974,12 +5006,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>Test Jerin</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -4994,7 +5026,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -5004,12 +5036,12 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -5021,27 +5053,27 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud: Azure</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>0-2 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bangalore </t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -5051,12 +5083,12 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5065,732 +5097,8 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Rubrik India</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer (CPD) - Winter Intern</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Rubrik India</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer - IAM</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="inlineStr">
-        <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>Scaler</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>Remote Instructor- Python</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G105" s="3" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>https://www.scaler.com/careers/</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>ShareChat</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr"/>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="inlineStr">
-        <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>https://sharechat.com/careers</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>ShareChat</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>AI Screenplay Writer</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="inlineStr">
-        <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>https://sharechat.com/careers</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>ShareChat</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>AI Video Editor</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr"/>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="inlineStr">
-        <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>https://sharechat.com/careers</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>ShareChat</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>AI Sound Designer</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr"/>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="inlineStr">
-        <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>https://sharechat.com/careers</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>ShareChat</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>AI Animator</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr"/>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="inlineStr">
-        <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>https://sharechat.com/careers</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Shipsy</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>QA Engineer</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>QA / SDET</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Shipsy</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Full Stack</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G112" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>SirionLabs</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Intern- Employee Engagement</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr"/>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G113" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sirionlabs.com/careers/</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Sprinklr</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Internship and Early Careers</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr"/>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G114" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sprinklr.com/careers/</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Stripe India</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer, Intern</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/stripe</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Thoughtworks India</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Software Procurement Intern</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>Gurgaon, India; Pune, India</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G116" s="3" t="inlineStr">
-        <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8236673?gh_jid=8236673</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/thoughtworks</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>Test Jerin</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G117" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I118"/>
+  <autoFilter ref="A1:I102"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -5893,22 +5201,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId117"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5920,7 +5212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5968,19 +5260,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INDmoney</t>
+          <t>Plivo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.indmoney.com/careers</t>
+          <t>https://www.plivo.com/careers/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
-  - navigating to "https://www.indmoney.com/careers", waiting until "networkidle"
+  - navigating to "https://www.plivo.com/careers/", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -6028,15 +5320,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Zluri</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.zluri.com/careers</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.zluri.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6045,18 +5357,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Blinkit</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://blinkit.com/careers</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6065,18 +5377,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Capillary Technologies</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://www.capillarytech.com/careers/</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6085,18 +5397,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6105,18 +5417,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Cleartrip</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://www.cleartrip.com/careers</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6125,18 +5437,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -6145,18 +5457,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6165,58 +5477,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>LatentView Analytics</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://www.latentview.com/careers/</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.latentview.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lenskart</t>
+          <t>MakeMyTrip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.lenskart.com/careers</t>
+          <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.lenskart.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MakeMyTrip</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://careers.makemytrip.com/</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6225,18 +5497,58 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FirstCry</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.firstcry.com/careers</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Netcore Cloud</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://netcorecloud.com/careers/</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://netcorecloud.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>OYO</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>https://www.oyorooms.com/careers/</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6245,18 +5557,38 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ninjacart</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://ninjacart.com/careers/</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://ninjacart.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -6265,18 +5597,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Swiggy</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>https://careers.swiggy.com/</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6285,18 +5617,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -6305,18 +5637,18 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -6325,18 +5657,18 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
